--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487881_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487881_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>P. UNIACKE</t>
+          <t>A. LAFUENTE SISO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.0521</v>
+        <v>5.3956</v>
       </c>
       <c r="E2" t="n">
-        <v>2.1114</v>
+        <v>5.7263</v>
       </c>
       <c r="F2" t="n">
-        <v>2.9406</v>
+        <v>-0.3307</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8563</v>
+        <v>5.9031</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.7937</v>
+        <v>-0.1449</v>
       </c>
       <c r="I2" t="n">
-        <v>1.65</v>
+        <v>6.0481</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.5193</v>
+        <v>7.9201</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.5977</v>
+        <v>1.7373</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0784</v>
+        <v>6.1827</v>
       </c>
       <c r="M2" t="n">
-        <v>1.3756</v>
+        <v>-2.0169</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.196</v>
+        <v>-1.8823</v>
       </c>
       <c r="O2" t="n">
-        <v>1.5716</v>
+        <v>-0.1347</v>
       </c>
       <c r="P2" t="n">
-        <v>1.4568</v>
+        <v>-1.6649</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-3.1218</v>
       </c>
       <c r="R2" t="n">
         <v>1.4568</v>
       </c>
       <c r="S2" t="n">
-        <v>2.3852</v>
+        <v>0.2199</v>
       </c>
       <c r="T2" t="n">
-        <v>2.4008</v>
+        <v>-0.2395</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0156</v>
+        <v>0.4594</v>
       </c>
       <c r="V2" t="n">
-        <v>0.3538</v>
+        <v>0.9376</v>
       </c>
       <c r="W2" t="n">
-        <v>0.23</v>
+        <v>1.1675</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1238</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. LAFUENTE SISO</t>
+          <t>P. UNIACKE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.7961</v>
+        <v>3.3045</v>
       </c>
       <c r="E3" t="n">
-        <v>4.8038</v>
+        <v>0.5693</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0077</v>
+        <v>2.7351</v>
       </c>
       <c r="G3" t="n">
-        <v>5.9031</v>
+        <v>0.8563</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.1449</v>
+        <v>-0.7937</v>
       </c>
       <c r="I3" t="n">
-        <v>6.0481</v>
+        <v>1.65</v>
       </c>
       <c r="J3" t="n">
-        <v>7.9201</v>
+        <v>-0.5193</v>
       </c>
       <c r="K3" t="n">
-        <v>1.7373</v>
+        <v>-0.5977</v>
       </c>
       <c r="L3" t="n">
-        <v>6.1827</v>
+        <v>0.0784</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.0169</v>
+        <v>1.3756</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.8823</v>
+        <v>-0.196</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.1347</v>
+        <v>1.5716</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.6649</v>
+        <v>1.4568</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.1218</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>1.4568</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3797</v>
+        <v>0.6375999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.162</v>
+        <v>0.8587</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7823</v>
+        <v>-0.2211</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9376</v>
+        <v>0.3538</v>
       </c>
       <c r="W3" t="n">
-        <v>1.1675</v>
+        <v>0.23</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.23</v>
+        <v>0.1238</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>W. LEVEQUE</t>
+          <t>A. MAZAIRA GOMEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.025</v>
+        <v>2.7572</v>
       </c>
       <c r="E4" t="n">
-        <v>3.8118</v>
+        <v>1.5432</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.7868000000000001</v>
+        <v>1.2141</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.6719</v>
+        <v>0.179</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.431</v>
+        <v>-1.4604</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.2409</v>
+        <v>1.6394</v>
       </c>
       <c r="J4" t="n">
-        <v>1.7942</v>
+        <v>1.1264</v>
       </c>
       <c r="K4" t="n">
-        <v>1.4023</v>
+        <v>0.279</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3919</v>
+        <v>0.8474</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.4661</v>
+        <v>-0.9474</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.8332</v>
+        <v>-1.7394</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.6328</v>
+        <v>0.792</v>
       </c>
       <c r="P4" t="n">
+        <v>0.2081</v>
+      </c>
+      <c r="Q4" t="n">
         <v>-2.0812</v>
       </c>
-      <c r="Q4" t="n">
-        <v>-3.1218</v>
-      </c>
       <c r="R4" t="n">
-        <v>1.0406</v>
+        <v>2.2893</v>
       </c>
       <c r="S4" t="n">
-        <v>2.1079</v>
+        <v>-0.1949</v>
       </c>
       <c r="T4" t="n">
-        <v>1.1769</v>
+        <v>-0.06710000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9311</v>
+        <v>-0.1278</v>
       </c>
       <c r="V4" t="n">
-        <v>4.6701</v>
+        <v>2.565</v>
       </c>
       <c r="W4" t="n">
-        <v>3.9625</v>
+        <v>2.565</v>
       </c>
       <c r="X4" t="n">
-        <v>0.7076</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. MAZAIRA GOMEZ</t>
+          <t>A. PALAZUELOS PEREZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2937</v>
+        <v>2.316</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5788</v>
+        <v>3.1263</v>
       </c>
       <c r="F5" t="n">
-        <v>0.715</v>
+        <v>-0.8103</v>
       </c>
       <c r="G5" t="n">
-        <v>0.179</v>
+        <v>2.1023</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.4604</v>
+        <v>-1.1552</v>
       </c>
       <c r="I5" t="n">
-        <v>1.6394</v>
+        <v>3.2575</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1264</v>
+        <v>4.1112</v>
       </c>
       <c r="K5" t="n">
-        <v>0.279</v>
+        <v>0.8250999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8474</v>
+        <v>3.2861</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.9474</v>
+        <v>-2.0088</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.7394</v>
+        <v>-1.9803</v>
       </c>
       <c r="O5" t="n">
-        <v>0.792</v>
+        <v>-0.0286</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2081</v>
+        <v>0.6244</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.0812</v>
+        <v>-1.0406</v>
       </c>
       <c r="R5" t="n">
-        <v>2.2893</v>
+        <v>1.6649</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.6584</v>
+        <v>-0.6407</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.0315</v>
+        <v>-0.1743</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6269</v>
+        <v>-0.4664</v>
       </c>
       <c r="V5" t="n">
-        <v>2.565</v>
+        <v>0.23</v>
       </c>
       <c r="W5" t="n">
-        <v>2.565</v>
+        <v>0.23</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. PALAZUELOS PEREZ</t>
+          <t>W. LEVEQUE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0771</v>
+        <v>1.4249</v>
       </c>
       <c r="E6" t="n">
-        <v>2.269</v>
+        <v>2.7402</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.192</v>
+        <v>-1.3153</v>
       </c>
       <c r="G6" t="n">
-        <v>2.1023</v>
+        <v>-1.6719</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.1552</v>
+        <v>-0.431</v>
       </c>
       <c r="I6" t="n">
-        <v>3.2575</v>
+        <v>-1.2409</v>
       </c>
       <c r="J6" t="n">
-        <v>4.1112</v>
+        <v>1.7942</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8250999999999999</v>
+        <v>1.4023</v>
       </c>
       <c r="L6" t="n">
-        <v>3.2861</v>
+        <v>0.3919</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.0088</v>
+        <v>-3.4661</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.9803</v>
+        <v>-1.8332</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0286</v>
+        <v>-1.6328</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6244</v>
+        <v>-2.0812</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0406</v>
+        <v>-3.1218</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6649</v>
+        <v>1.0406</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.8796</v>
+        <v>0.5079</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.0315</v>
+        <v>0.1053</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.8481</v>
+        <v>0.4026</v>
       </c>
       <c r="V6" t="n">
-        <v>0.23</v>
+        <v>4.6701</v>
       </c>
       <c r="W6" t="n">
-        <v>0.23</v>
+        <v>3.9625</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.7076</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. USAOLA REDONDO</t>
+          <t>P. MENDES LIMA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1902</v>
+        <v>-0.0566</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0392</v>
+        <v>0.5546</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2294</v>
+        <v>-0.6112</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.0669</v>
+        <v>-0.1132</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1429</v>
+        <v>0.175</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2098</v>
+        <v>-0.2882</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0392</v>
+        <v>1.0627</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1.2856</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0392</v>
+        <v>-0.2229</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1061</v>
+        <v>-1.1759</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1429</v>
+        <v>-1.1106</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.249</v>
+        <v>-0.0653</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.6649</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.6649</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1233</v>
+        <v>-1.3784</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>-0.5081</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1233</v>
+        <v>-0.8703</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.23</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. STRIKKER</t>
+          <t>A. USAOLA REDONDO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5683</v>
+        <v>-0.1609</v>
       </c>
       <c r="E8" t="n">
-        <v>0.272</v>
+        <v>0.0392</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8403</v>
+        <v>-0.2001</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.0145</v>
+        <v>-0.0669</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1385</v>
+        <v>0.1429</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.876</v>
+        <v>-0.2098</v>
       </c>
       <c r="J8" t="n">
-        <v>1.2351</v>
+        <v>0.0392</v>
       </c>
       <c r="K8" t="n">
-        <v>1.262</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.027</v>
+        <v>0.0392</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.2495</v>
+        <v>-0.1061</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.4005</v>
+        <v>0.1429</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8491</v>
+        <v>-0.249</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.8325</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.2487</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.8188</v>
+        <v>-0.0939</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6582</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1605</v>
+        <v>-0.0939</v>
       </c>
       <c r="V8" t="n">
-        <v>0.4599</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.4599</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. MENDES LIMA</t>
+          <t>M. STRIKKER</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6869</v>
+        <v>-0.8729</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0464</v>
+        <v>-0.0914</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6405</v>
+        <v>-0.7816</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1132</v>
+        <v>-1.0145</v>
       </c>
       <c r="H9" t="n">
-        <v>0.175</v>
+        <v>-0.1385</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2882</v>
+        <v>-0.876</v>
       </c>
       <c r="J9" t="n">
-        <v>1.0627</v>
+        <v>1.2351</v>
       </c>
       <c r="K9" t="n">
-        <v>1.2856</v>
+        <v>1.262</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.2229</v>
+        <v>-0.027</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.1759</v>
+        <v>-2.2495</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.1106</v>
+        <v>-1.4005</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0653</v>
+        <v>-0.8491</v>
       </c>
       <c r="P9" t="n">
-        <v>1.6649</v>
+        <v>-0.8325</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-2.0812</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6649</v>
+        <v>1.2487</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.0088</v>
+        <v>0.5141</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.1091</v>
+        <v>0.2948</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.8996</v>
+        <v>0.2193</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.23</v>
+        <v>0.4599</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.4599</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.7485</v>
+        <v>-3.7317</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.8968</v>
+        <v>-3.9388</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1484</v>
+        <v>0.2071</v>
       </c>
       <c r="G10" t="n">
         <v>-1.0924</v>
@@ -1234,13 +1234,13 @@
         <v>1.6649</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3647</v>
+        <v>-0.3479</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1272</v>
+        <v>0.0853</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4919</v>
+        <v>-0.4332</v>
       </c>
       <c r="V10" t="n">
         <v>-1.8751</v>
@@ -1267,19 +1267,19 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>10.0501</v>
+        <v>10.3761</v>
       </c>
       <c r="E11" t="n">
-        <v>9.942800000000002</v>
+        <v>10.2689</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1073000000000003</v>
+        <v>0.1070999999999999</v>
       </c>
       <c r="G11" t="n">
         <v>5.081800000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>-5.2664</v>
+        <v>-5.266399999999999</v>
       </c>
       <c r="I11" t="n">
         <v>10.3483</v>
@@ -1300,7 +1300,7 @@
         <v>-10.1464</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.3060999999999999</v>
+        <v>-0.3060999999999994</v>
       </c>
       <c r="P11" t="n">
         <v>-1.0406</v>
@@ -1312,19 +1312,19 @@
         <v>12.4869</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1026</v>
+        <v>-0.7763000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>0.02899999999999972</v>
+        <v>0.3551</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.1315</v>
+        <v>-1.1314</v>
       </c>
       <c r="V11" t="n">
-        <v>7.111299999999998</v>
+        <v>7.1113</v>
       </c>
       <c r="W11" t="n">
-        <v>7.9073</v>
+        <v>7.907299999999998</v>
       </c>
       <c r="X11" t="n">
         <v>-0.7961</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.0744</v>
+        <v>2.9824</v>
       </c>
       <c r="E12" t="n">
         <v>4.3758</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.3014</v>
+        <v>-1.3934</v>
       </c>
       <c r="G12" t="n">
         <v>1.6713</v>
@@ -1390,13 +1390,13 @@
         <v>1.6649</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1696</v>
+        <v>0.0776</v>
       </c>
       <c r="T12" t="n">
         <v>-0.019</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1886</v>
+        <v>0.09660000000000001</v>
       </c>
       <c r="V12" t="n">
         <v>0.8173</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8332000000000001</v>
+        <v>1.2198</v>
       </c>
       <c r="E13" t="n">
-        <v>1.064</v>
+        <v>1.2783</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.2308</v>
+        <v>-0.0585</v>
       </c>
       <c r="G13" t="n">
         <v>-0.4103</v>
@@ -1468,13 +1468,13 @@
         <v>1.4568</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2133</v>
+        <v>0.1732</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4567</v>
+        <v>-0.2424</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2434</v>
+        <v>0.4156</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. SANTA BARBARA CARCELEN</t>
+          <t>I. CASAS GARRIDO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3771</v>
+        <v>0.1355</v>
       </c>
       <c r="E14" t="n">
-        <v>2.3118</v>
+        <v>0.4666</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.9347</v>
+        <v>-0.3311</v>
       </c>
       <c r="G14" t="n">
-        <v>1.4107</v>
+        <v>-1.1325</v>
       </c>
       <c r="H14" t="n">
-        <v>3.2109</v>
+        <v>-1.5799</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.8002</v>
+        <v>0.4474</v>
       </c>
       <c r="J14" t="n">
-        <v>3.7377</v>
+        <v>0.1127</v>
       </c>
       <c r="K14" t="n">
-        <v>3.7949</v>
+        <v>-1.045</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.0572</v>
+        <v>1.1577</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.327</v>
+        <v>-1.2452</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.5839</v>
+        <v>-0.5349</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.7431</v>
+        <v>-0.7103</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.6244</v>
+        <v>1.2487</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4568</v>
+        <v>1.2487</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6309</v>
+        <v>0.3696</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4253</v>
+        <v>0.3539</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2056</v>
+        <v>0.0157</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.0401</v>
+        <v>-0.3503</v>
       </c>
       <c r="W14" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.2701</v>
+        <v>-0.3503</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>I. CASAS GARRIDO</t>
+          <t>J. SANTA BARBARA CARCELEN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2324</v>
+        <v>0.0747</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6808999999999999</v>
+        <v>2.0975</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4485</v>
+        <v>-2.0228</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.1325</v>
+        <v>1.4107</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.5799</v>
+        <v>3.2109</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4474</v>
+        <v>-1.8002</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1127</v>
+        <v>3.7377</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.045</v>
+        <v>3.7949</v>
       </c>
       <c r="L15" t="n">
-        <v>1.1577</v>
+        <v>-0.0572</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.2452</v>
+        <v>-2.327</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.5349</v>
+        <v>-0.5839</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.7103</v>
+        <v>-1.7431</v>
       </c>
       <c r="P15" t="n">
-        <v>1.2487</v>
+        <v>-0.6244</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-2.0812</v>
       </c>
       <c r="R15" t="n">
-        <v>1.2487</v>
+        <v>1.4568</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4664</v>
+        <v>0.3285</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5682</v>
+        <v>0.211</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1017</v>
+        <v>0.1175</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.3503</v>
+        <v>-1.0401</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.3503</v>
+        <v>-1.2701</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. CAÑETE PUENTENUEVA</t>
+          <t>J. MARTINEZ MEGIAS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0509</v>
+        <v>-0.2401</v>
       </c>
       <c r="E16" t="n">
-        <v>0.849</v>
+        <v>2.1957</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.798</v>
+        <v>-2.4358</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.2045</v>
+        <v>1.1811</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6161</v>
+        <v>0.55</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.8206</v>
+        <v>0.6311</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.2413</v>
+        <v>2.4957</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1875</v>
+        <v>1.0849</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.4287</v>
+        <v>1.4108</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0367</v>
+        <v>-1.3146</v>
       </c>
       <c r="N16" t="n">
-        <v>0.4286</v>
+        <v>-0.5349</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.3919</v>
+        <v>-0.7796999999999999</v>
       </c>
       <c r="P16" t="n">
-        <v>0.2081</v>
+        <v>1.2487</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.2081</v>
       </c>
       <c r="R16" t="n">
-        <v>0.2081</v>
+        <v>1.4568</v>
       </c>
       <c r="S16" t="n">
-        <v>2.2149</v>
+        <v>-0.1049</v>
       </c>
       <c r="T16" t="n">
-        <v>2.0903</v>
+        <v>-0.0919</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1246</v>
+        <v>-0.013</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.1675</v>
+        <v>-2.565</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.1675</v>
+        <v>-2.565</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. MORENO POZA</t>
+          <t>K. FELIZOR</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4217</v>
+        <v>-0.2872</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0461</v>
+        <v>-0.1744</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3756</v>
+        <v>-0.1128</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.1361</v>
+        <v>-0.3396</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.8871</v>
+        <v>1.0875</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.249</v>
+        <v>-1.4271</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.6952</v>
+        <v>1.7262</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.6952</v>
+        <v>1.6266</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>0.09959999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.4409</v>
+        <v>-2.0658</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1919</v>
+        <v>-0.5391</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.249</v>
+        <v>-1.5267</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2081</v>
+        <v>0.4162</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.2487</v>
       </c>
       <c r="R17" t="n">
-        <v>0.2081</v>
+        <v>1.6649</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5063</v>
+        <v>0.1103</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6491</v>
+        <v>-0.1743</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1429</v>
+        <v>0.2845</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.4741</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>-0.4776</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>0.0035</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>K. FELIZOR</t>
+          <t>J. MORENO POZA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9174</v>
+        <v>-0.636</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.603</v>
+        <v>-0.2604</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3144</v>
+        <v>-0.3756</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.3396</v>
+        <v>-1.1361</v>
       </c>
       <c r="H18" t="n">
-        <v>1.0875</v>
+        <v>-0.8871</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.4271</v>
+        <v>-0.249</v>
       </c>
       <c r="J18" t="n">
-        <v>1.7262</v>
+        <v>-0.6952</v>
       </c>
       <c r="K18" t="n">
-        <v>1.6266</v>
+        <v>-0.6952</v>
       </c>
       <c r="L18" t="n">
-        <v>0.09959999999999999</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.0658</v>
+        <v>-0.4409</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5391</v>
+        <v>-0.1919</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.5267</v>
+        <v>-0.249</v>
       </c>
       <c r="P18" t="n">
-        <v>0.4162</v>
+        <v>0.2081</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.2487</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.6649</v>
+        <v>0.2081</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.52</v>
+        <v>0.2919</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6029</v>
+        <v>0.4348</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0829</v>
+        <v>-0.1429</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.4741</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.4776</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.0035</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. MARTINEZ MEGIAS</t>
+          <t>F. LOPEZ JIMENEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9481000000000001</v>
+        <v>-1.0104</v>
       </c>
       <c r="E19" t="n">
-        <v>1.6599</v>
+        <v>-0.8016</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.608</v>
+        <v>-0.2087</v>
       </c>
       <c r="G19" t="n">
-        <v>1.1811</v>
+        <v>-1.0741</v>
       </c>
       <c r="H19" t="n">
-        <v>0.55</v>
+        <v>-0.3687</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6311</v>
+        <v>-0.7054</v>
       </c>
       <c r="J19" t="n">
-        <v>2.4957</v>
+        <v>-0.6168</v>
       </c>
       <c r="K19" t="n">
-        <v>1.0849</v>
+        <v>0.0192</v>
       </c>
       <c r="L19" t="n">
-        <v>1.4108</v>
+        <v>-0.636</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.3146</v>
+        <v>-0.4573</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5349</v>
+        <v>-0.3879</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.7796999999999999</v>
+        <v>-0.0694</v>
       </c>
       <c r="P19" t="n">
-        <v>1.2487</v>
+        <v>0.2081</v>
       </c>
       <c r="Q19" t="n">
         <v>-0.2081</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4568</v>
+        <v>0.4162</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8129</v>
+        <v>-0.3743</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6277</v>
+        <v>-0.2067</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1852</v>
+        <v>-0.1677</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.565</v>
+        <v>0.23</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.565</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>F. LOPEZ JIMENEZ</t>
+          <t>A. CAÑETE PUENTENUEVA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.2349</v>
+        <v>-1.2158</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9088000000000001</v>
+        <v>-0.3297</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3262</v>
+        <v>-0.8861</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.0741</v>
+        <v>-1.2045</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3687</v>
+        <v>0.6161</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.7054</v>
+        <v>-1.8206</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.6168</v>
+        <v>-1.2413</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0192</v>
+        <v>0.1875</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.636</v>
+        <v>-1.4287</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.4573</v>
+        <v>0.0367</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3879</v>
+        <v>0.4286</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.0694</v>
+        <v>-0.3919</v>
       </c>
       <c r="P20" t="n">
         <v>0.2081</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.2081</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4162</v>
+        <v>0.2081</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5989</v>
+        <v>0.9481000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3138</v>
+        <v>0.9115</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2851</v>
+        <v>0.0365</v>
       </c>
       <c r="V20" t="n">
-        <v>0.23</v>
+        <v>-1.1675</v>
       </c>
       <c r="W20" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.7875</v>
+        <v>-1.5756</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.2562</v>
+        <v>-0.3634</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.5313</v>
+        <v>-1.2123</v>
       </c>
       <c r="G21" t="n">
         <v>-1.3276</v>
@@ -2092,13 +2092,13 @@
         <v>2.0812</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3503</v>
+        <v>0.5622</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3725</v>
+        <v>0.2653</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0221</v>
+        <v>0.2969</v>
       </c>
       <c r="V21" t="n">
         <v>-0.8102</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.8066</v>
+        <v>-1.8168</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.7625</v>
+        <v>-1.6554</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.044</v>
+        <v>-0.1615</v>
       </c>
       <c r="G22" t="n">
         <v>0.8556</v>
@@ -2170,13 +2170,13 @@
         <v>0.6244</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0378</v>
+        <v>-0.0481</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2486</v>
+        <v>-0.1414</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2108</v>
+        <v>0.09329999999999999</v>
       </c>
       <c r="V22" t="n">
         <v>-1.1675</v>
@@ -2203,10 +2203,10 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.5017</v>
+        <v>-6.966</v>
       </c>
       <c r="E23" t="n">
-        <v>-7.4719</v>
+        <v>-6.9361</v>
       </c>
       <c r="F23" t="n">
         <v>-0.0298</v>
@@ -2248,10 +2248,10 @@
         <v>1.0406</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.053</v>
+        <v>-0.5172</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7053</v>
+        <v>-0.1695</v>
       </c>
       <c r="U23" t="n">
         <v>-0.3477</v>
@@ -2281,19 +2281,19 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-10.0499</v>
+        <v>-9.3355</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.1071</v>
+        <v>-0.1071000000000009</v>
       </c>
       <c r="F24" t="n">
-        <v>-9.9427</v>
+        <v>-9.228400000000001</v>
       </c>
       <c r="G24" t="n">
         <v>-5.0817</v>
       </c>
       <c r="H24" t="n">
-        <v>5.2665</v>
+        <v>5.266500000000001</v>
       </c>
       <c r="I24" t="n">
         <v>-10.3482</v>
@@ -2326,13 +2326,13 @@
         <v>13.5275</v>
       </c>
       <c r="S24" t="n">
-        <v>1.1025</v>
+        <v>1.8169</v>
       </c>
       <c r="T24" t="n">
-        <v>1.1314</v>
+        <v>1.1313</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.02879999999999999</v>
+        <v>0.6852999999999999</v>
       </c>
       <c r="V24" t="n">
         <v>-7.1112</v>
